--- a/artfynd/A 37975-2025 artfynd.xlsx
+++ b/artfynd/A 37975-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AY12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1693,6 +1693,103 @@
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>129746484</v>
+      </c>
+      <c r="B12" t="n">
+        <v>91587</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Vitterknulen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>600022</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6960231</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 37975-2025 artfynd.xlsx
+++ b/artfynd/A 37975-2025 artfynd.xlsx
@@ -1698,7 +1698,7 @@
         <v>129746484</v>
       </c>
       <c r="B12" t="n">
-        <v>91587</v>
+        <v>91588</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 37975-2025 artfynd.xlsx
+++ b/artfynd/A 37975-2025 artfynd.xlsx
@@ -1698,7 +1698,7 @@
         <v>129746484</v>
       </c>
       <c r="B12" t="n">
-        <v>91588</v>
+        <v>91593</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 37975-2025 artfynd.xlsx
+++ b/artfynd/A 37975-2025 artfynd.xlsx
@@ -1698,7 +1698,7 @@
         <v>129746484</v>
       </c>
       <c r="B12" t="n">
-        <v>91593</v>
+        <v>91597</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 37975-2025 artfynd.xlsx
+++ b/artfynd/A 37975-2025 artfynd.xlsx
@@ -1698,7 +1698,7 @@
         <v>129746484</v>
       </c>
       <c r="B12" t="n">
-        <v>91597</v>
+        <v>91599</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 37975-2025 artfynd.xlsx
+++ b/artfynd/A 37975-2025 artfynd.xlsx
@@ -1698,7 +1698,7 @@
         <v>129746484</v>
       </c>
       <c r="B12" t="n">
-        <v>91599</v>
+        <v>91602</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 37975-2025 artfynd.xlsx
+++ b/artfynd/A 37975-2025 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>112538820</v>
       </c>
       <c r="B2" t="n">
-        <v>79676</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>81312</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -777,15 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>112538825</v>
+        <v>129746484</v>
       </c>
       <c r="B3" t="n">
-        <v>78809</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>600035</v>
+        <v>600022</v>
       </c>
       <c r="R3" t="n">
-        <v>6960106</v>
+        <v>6960231</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -847,12 +837,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -867,27 +857,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Rasmus Viding</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Rasmus Viding</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>112538817</v>
+        <v>112538818</v>
       </c>
       <c r="B4" t="n">
-        <v>78312</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -895,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>229821</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>599974</v>
+        <v>599991</v>
       </c>
       <c r="R4" t="n">
-        <v>6960414</v>
+        <v>6960346</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -984,16 +969,11 @@
         <v>112538821</v>
       </c>
       <c r="B5" t="n">
-        <v>77746</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1083,37 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>112538816</v>
+        <v>112538824</v>
       </c>
       <c r="B6" t="n">
-        <v>78767</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>229497</v>
+        <v>6446</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>599956</v>
+        <v>600034</v>
       </c>
       <c r="R6" t="n">
-        <v>6960483</v>
+        <v>6960184</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1188,12 +1163,7 @@
         <v>112538822</v>
       </c>
       <c r="B7" t="n">
-        <v>78338</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1287,15 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>112538824</v>
+        <v>112538825</v>
       </c>
       <c r="B8" t="n">
-        <v>77498</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1303,21 +1268,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1330,7 +1295,7 @@
         <v>600034</v>
       </c>
       <c r="R8" t="n">
-        <v>6960184</v>
+        <v>6960106</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1392,12 +1357,7 @@
         <v>112538826</v>
       </c>
       <c r="B9" t="n">
-        <v>78842</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80467</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1429,7 +1389,7 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>600035</v>
+        <v>600034</v>
       </c>
       <c r="R9" t="n">
         <v>6960106</v>
@@ -1494,12 +1454,7 @@
         <v>112538823</v>
       </c>
       <c r="B10" t="n">
-        <v>77499</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79085</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1593,15 +1548,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>112538818</v>
+        <v>112538816</v>
       </c>
       <c r="B11" t="n">
-        <v>90922</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80392</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1609,21 +1559,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4364</v>
+        <v>229497</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1633,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>599991</v>
+        <v>599956</v>
       </c>
       <c r="R11" t="n">
-        <v>6960347</v>
+        <v>6960483</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1695,10 +1645,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129746484</v>
+        <v>112538817</v>
       </c>
       <c r="B12" t="n">
-        <v>91638</v>
+        <v>79917</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1706,21 +1656,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>229821</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1730,10 +1680,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>600022</v>
+        <v>599974</v>
       </c>
       <c r="R12" t="n">
-        <v>6960231</v>
+        <v>6960414</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1760,12 +1710,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2023-10-01</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2023-10-01</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1780,12 +1730,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Rasmus Viding</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Rasmus Viding</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>

--- a/artfynd/A 37975-2025 artfynd.xlsx
+++ b/artfynd/A 37975-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AZ12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112538820</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129746484</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112538818</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112538821</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112538824</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112538822</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112538825</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1448,6 +1488,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112538826</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1545,6 +1590,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112538823</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1642,6 +1692,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112538816</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1739,8 +1794,26 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112538817</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>